--- a/NECP Scenario/Results/Regional Results/Crete_Generation.xlsx
+++ b/NECP Scenario/Results/Regional Results/Crete_Generation.xlsx
@@ -563,25 +563,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3.997866090271769E-08</v>
+        <v>5.903335147255001E-08</v>
       </c>
       <c r="C3">
-        <v>4.775086476970248E-08</v>
+        <v>7.076254007614091E-08</v>
       </c>
       <c r="D3">
-        <v>3.452809016362223E-07</v>
+        <v>5.419295276558744E-07</v>
       </c>
       <c r="E3">
-        <v>1.349366933732124E-05</v>
+        <v>0.08950432068646588</v>
       </c>
       <c r="F3">
-        <v>2.079736365077354</v>
+        <v>1.916031439868015</v>
       </c>
       <c r="G3">
-        <v>3.305743107759628</v>
+        <v>3.255914360609448</v>
       </c>
       <c r="H3">
-        <v>5.053561946937828</v>
+        <v>5.016846028928486</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -589,25 +589,25 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>3.398186176834463E-08</v>
+        <v>5.017834875251687E-08</v>
       </c>
       <c r="C4">
-        <v>4.058823505646901E-08</v>
+        <v>6.014815906651985E-08</v>
       </c>
       <c r="D4">
-        <v>2.934887663930111E-07</v>
+        <v>4.606400985092936E-07</v>
       </c>
       <c r="E4">
-        <v>1.146961893672529E-05</v>
+        <v>0.07607867258348872</v>
       </c>
       <c r="F4">
-        <v>1.767775910309073</v>
+        <v>1.628626723885058</v>
       </c>
       <c r="G4">
-        <v>2.809881641620606</v>
+        <v>2.767527206522558</v>
       </c>
       <c r="H4">
-        <v>4.295527654898279</v>
+        <v>4.264319124589786</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -849,25 +849,25 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>2.906710488883712</v>
+        <v>2.906710490288309</v>
       </c>
       <c r="C14">
-        <v>2.955099069893503</v>
+        <v>2.955099070845101</v>
       </c>
       <c r="D14">
-        <v>3.037823626940756</v>
+        <v>2.632910284064862</v>
       </c>
       <c r="E14">
-        <v>3.074858443122941</v>
+        <v>2.89653883335572</v>
       </c>
       <c r="F14">
-        <v>3.69627979299459</v>
+        <v>3.696279820488713</v>
       </c>
       <c r="G14">
-        <v>4.604097105714256</v>
+        <v>4.604097148786788</v>
       </c>
       <c r="H14">
-        <v>6.071135588195071</v>
+        <v>6.071135848322767</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1193,19 +1193,19 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>7.947051560046368E-08</v>
+        <v>1.171505753594956E-07</v>
       </c>
       <c r="E27">
-        <v>4.239615764440608E-07</v>
+        <v>6.774801122791775E-07</v>
       </c>
       <c r="F27">
-        <v>0.5485132432507328</v>
+        <v>1.085427063136814</v>
       </c>
       <c r="G27">
-        <v>1.283178671352275</v>
+        <v>1.647161234526571</v>
       </c>
       <c r="H27">
-        <v>1.683409493673159</v>
+        <v>1.843337484206112</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1213,25 +1213,25 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>5.817911052651522</v>
+        <v>5.81791109333977</v>
       </c>
       <c r="C28">
-        <v>2.124034765240894</v>
+        <v>2.124034777004868</v>
       </c>
       <c r="D28">
-        <v>0.003759700397827538</v>
+        <v>0.007867130296537843</v>
       </c>
       <c r="E28">
-        <v>1.138327038071561E-07</v>
+        <v>1.69320216975695E-07</v>
       </c>
       <c r="F28">
-        <v>1.07274696540839E-07</v>
+        <v>1.582806009087565E-07</v>
       </c>
       <c r="G28">
-        <v>0.02043181628512926</v>
+        <v>0.02042751341687906</v>
       </c>
       <c r="H28">
-        <v>0.03187757474375544</v>
+        <v>0.03068931473323512</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1239,25 +1239,25 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>2.326344782493396</v>
+        <v>2.326344792607603</v>
       </c>
       <c r="C29">
-        <v>0.8708563892250021</v>
+        <v>0.8708563894939184</v>
       </c>
       <c r="D29">
-        <v>0.00156003825169107</v>
+        <v>0.003264364333333619</v>
       </c>
       <c r="E29">
-        <v>4.302959786326227E-08</v>
+        <v>6.401488047872354E-08</v>
       </c>
       <c r="F29">
-        <v>4.045570440857838E-08</v>
+        <v>5.969145538923165E-08</v>
       </c>
       <c r="G29">
-        <v>0.007814687086323416</v>
+        <v>0.007809222863959878</v>
       </c>
       <c r="H29">
-        <v>0.01209034197694385</v>
+        <v>0.01165327023716245</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1271,19 +1271,19 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>1.605441798275536</v>
+        <v>1.445176728686637</v>
       </c>
       <c r="E30">
-        <v>1.9267473031404</v>
+        <v>1.902289622147872</v>
       </c>
       <c r="F30">
-        <v>3.365727772740574</v>
+        <v>3.034882371273461</v>
       </c>
       <c r="G30">
-        <v>4.445053494573993</v>
+        <v>4.065486730011843</v>
       </c>
       <c r="H30">
-        <v>5.328298892963208</v>
+        <v>5.326342424990004</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1291,25 +1291,25 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>0.1299380469776903</v>
+        <v>0.1299380466060347</v>
       </c>
       <c r="C31">
-        <v>0.1299380424065202</v>
+        <v>0.1299380398512893</v>
       </c>
       <c r="D31">
-        <v>0.1299327817643622</v>
+        <v>0.1299379050409521</v>
       </c>
       <c r="E31">
-        <v>0.1299378750527052</v>
+        <v>0.1299377851801305</v>
       </c>
       <c r="F31">
-        <v>0.1299378784262633</v>
+        <v>0.1299377966978451</v>
       </c>
       <c r="G31">
-        <v>0.1298778926084388</v>
+        <v>0.1299378202100618</v>
       </c>
       <c r="H31">
-        <v>0.1297829992837596</v>
+        <v>0.129102542432661</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1323,19 +1323,19 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>0.2252414497575023</v>
+        <v>0.6302582483971539</v>
       </c>
       <c r="E32">
-        <v>0.8501893521118227</v>
+        <v>1.03461348594275</v>
       </c>
       <c r="F32">
-        <v>1.086090262650006</v>
+        <v>1.086090090914086</v>
       </c>
       <c r="G32">
-        <v>1.089099700203848</v>
+        <v>1.089099678600745</v>
       </c>
       <c r="H32">
-        <v>1.089099471662993</v>
+        <v>1.089099340949698</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1343,25 +1343,25 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>0.1693559607200766</v>
+        <v>0.1693559593281442</v>
       </c>
       <c r="C33">
-        <v>0.169355961669599</v>
+        <v>0.1693559607319848</v>
       </c>
       <c r="D33">
-        <v>0.1693559530636092</v>
+        <v>0.1692524993523872</v>
       </c>
       <c r="E33">
-        <v>0.1681002861517704</v>
+        <v>0.1619957621067093</v>
       </c>
       <c r="F33">
-        <v>0.1674834360742621</v>
+        <v>0.1674835803373345</v>
       </c>
       <c r="G33">
-        <v>0.169355914487001</v>
+        <v>0.1693558930388954</v>
       </c>
       <c r="H33">
-        <v>0.1693556874843289</v>
+        <v>0.1693555583134998</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1375,19 +1375,19 @@
         <v>0</v>
       </c>
       <c r="D34">
-        <v>1.610058540000214E-08</v>
+        <v>2.40025980719038E-08</v>
       </c>
       <c r="E34">
-        <v>2.677217317988366E-08</v>
+        <v>4.08574475565979E-08</v>
       </c>
       <c r="F34">
-        <v>3.963783585403171E-08</v>
+        <v>6.064837800943754E-08</v>
       </c>
       <c r="G34">
-        <v>5.484557368178222E-08</v>
+        <v>8.298874272386139E-08</v>
       </c>
       <c r="H34">
-        <v>3.179739098436312E-07</v>
+        <v>4.824859498921632E-07</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1395,25 +1395,25 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>0.0007703744411397995</v>
+        <v>0.0007703719178834364</v>
       </c>
       <c r="C35">
-        <v>0.000770345525277443</v>
+        <v>0.000770326310337761</v>
       </c>
       <c r="D35">
-        <v>0.0007697174447817739</v>
+        <v>0.0007695483941653608</v>
       </c>
       <c r="E35">
-        <v>0.0007693767667151958</v>
+        <v>0.0007689000778946478</v>
       </c>
       <c r="F35">
-        <v>0.0007688891525982224</v>
+        <v>0.0007681996398948929</v>
       </c>
       <c r="G35">
-        <v>0.0007678286558277351</v>
+        <v>0.0007666956935719676</v>
       </c>
       <c r="H35">
-        <v>0.0007553078284063573</v>
+        <v>0.0007399040497305899</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1427,19 +1427,19 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>2.96040746503387</v>
+        <v>2.662762169771177</v>
       </c>
       <c r="E36">
-        <v>4.052744744711471</v>
+        <v>3.672355785650228</v>
       </c>
       <c r="F36">
-        <v>4.118321375558563</v>
+        <v>3.805722772323056</v>
       </c>
       <c r="G36">
-        <v>4.119265991779355</v>
+        <v>3.774389262342671</v>
       </c>
       <c r="H36">
-        <v>4.09153411366958</v>
+        <v>3.605368653861765</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1447,25 +1447,25 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>0.5089779132244263</v>
+        <v>0.5089779103120073</v>
       </c>
       <c r="C37">
-        <v>0.5072325523055108</v>
+        <v>0.5072237649856305</v>
       </c>
       <c r="D37">
-        <v>0.4629470063421485</v>
+        <v>0.463296570515507</v>
       </c>
       <c r="E37">
-        <v>0.4422464252081296</v>
+        <v>0.4401422592952978</v>
       </c>
       <c r="F37">
-        <v>0.4472648942602536</v>
+        <v>0.4531693989964578</v>
       </c>
       <c r="G37">
-        <v>0.4515342287502773</v>
+        <v>0.4536245730601702</v>
       </c>
       <c r="H37">
-        <v>0.4537386503972405</v>
+        <v>0.440975233604599</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1473,25 +1473,25 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>1.50901023924111E-08</v>
+        <v>2.228936550211529E-08</v>
       </c>
       <c r="C38">
-        <v>0.001745408546527851</v>
+        <v>0.001754218574192784</v>
       </c>
       <c r="D38">
-        <v>0.2935160103567304</v>
+        <v>0.2670799504302822</v>
       </c>
       <c r="E38">
-        <v>0.5699090734400699</v>
+        <v>0.574873697247665</v>
       </c>
       <c r="F38">
-        <v>0.7516905077357233</v>
+        <v>0.9302048209361815</v>
       </c>
       <c r="G38">
-        <v>1.250863208073848</v>
+        <v>1.392871799403434</v>
       </c>
       <c r="H38">
-        <v>1.457516925892989</v>
+        <v>1.778922993144385</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1525,25 +1525,25 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>3.997866090271769E-08</v>
+        <v>5.903335147255001E-08</v>
       </c>
       <c r="C40">
-        <v>4.775086476970248E-08</v>
+        <v>7.076254007614091E-08</v>
       </c>
       <c r="D40">
-        <v>3.452809016362223E-07</v>
+        <v>5.419295276558744E-07</v>
       </c>
       <c r="E40">
-        <v>1.349366933732124E-05</v>
+        <v>0.08950432068646588</v>
       </c>
       <c r="F40">
-        <v>2.079736365077354</v>
+        <v>1.916031439868015</v>
       </c>
       <c r="G40">
-        <v>3.305743107759628</v>
+        <v>3.255914360609448</v>
       </c>
       <c r="H40">
-        <v>5.053561946937828</v>
+        <v>5.016846028928486</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1551,25 +1551,25 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>3.398186176834463E-08</v>
+        <v>5.017834875251687E-08</v>
       </c>
       <c r="C41">
-        <v>4.058823505646901E-08</v>
+        <v>6.014815906651985E-08</v>
       </c>
       <c r="D41">
-        <v>2.934887663930111E-07</v>
+        <v>4.606400985092936E-07</v>
       </c>
       <c r="E41">
-        <v>1.146961893672529E-05</v>
+        <v>0.07607867258348872</v>
       </c>
       <c r="F41">
-        <v>1.767775910309073</v>
+        <v>1.628626723885058</v>
       </c>
       <c r="G41">
-        <v>2.809881641620606</v>
+        <v>2.767527206522558</v>
       </c>
       <c r="H41">
-        <v>4.295527654898279</v>
+        <v>4.264319124589786</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1577,25 +1577,25 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>-5.996799134373065E-09</v>
+        <v>-8.855002720033145E-09</v>
       </c>
       <c r="C42">
-        <v>-7.162629713233472E-09</v>
+        <v>-1.061438100962106E-08</v>
       </c>
       <c r="D42">
-        <v>-5.17921352432112E-08</v>
+        <v>-8.12894291465808E-08</v>
       </c>
       <c r="E42">
-        <v>-2.024050400595957E-06</v>
+        <v>-0.01342564810297717</v>
       </c>
       <c r="F42">
-        <v>-0.311960454768281</v>
+        <v>-0.2874047159829567</v>
       </c>
       <c r="G42">
-        <v>-0.4958614661390217</v>
+        <v>-0.4883871540868903</v>
       </c>
       <c r="H42">
-        <v>-0.7580342920395484</v>
+        <v>-0.7525269043386995</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1606,22 +1606,22 @@
         <v>-0</v>
       </c>
       <c r="C43">
-        <v>1.506609891904631</v>
+        <v>1.506618705144014</v>
       </c>
       <c r="D43">
-        <v>-2.06123882335551</v>
+        <v>-2.018564199562573</v>
       </c>
       <c r="E43">
-        <v>-3.414833506450757</v>
+        <v>-3.176417614662238</v>
       </c>
       <c r="F43">
-        <v>-4.526859604157745</v>
+        <v>-4.450788903802859</v>
       </c>
       <c r="G43">
-        <v>-5.243573112279342</v>
+        <v>-4.892730193646199</v>
       </c>
       <c r="H43">
-        <v>-4.746539510730961</v>
+        <v>-4.409956510851192</v>
       </c>
     </row>
     <row r="44" spans="1:8">
